--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 05/XKSX_VoHopTG102LE_SL500_180526.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 05/XKSX_VoHopTG102LE_SL500_180526.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Xuất kho\Tháng 05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{347FBCDF-FB3B-4129-A38C-5D8304EE6FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{430675E6-A8C6-4855-BD02-16C45A6DC1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -114,11 +114,11 @@
     <t>Hà Nội, ngày 18 tháng 05 năm 2026</t>
   </si>
   <si>
-    <t>Lô 1/2026 
+    <t>VT_Vỏ hộp_TG102LE</t>
+  </si>
+  <si>
+    <t>Lô 2/2026 
 TG102LE-4G(8686)</t>
-  </si>
-  <si>
-    <t>VT_Vỏ hộp_TG102LE</t>
   </si>
 </sst>
 </file>
@@ -505,6 +505,12 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -560,12 +566,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -991,66 +991,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="45" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="47"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="39"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="48" t="s">
+      <c r="A2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="49"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="39"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="48" t="s">
+      <c r="A3" s="41"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="49"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="51"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="42"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="50" t="s">
+      <c r="A4" s="44"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="51"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="53"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="35"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="37"/>
     </row>
     <row r="6" spans="1:8" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
@@ -1117,25 +1117,25 @@
       </c>
     </row>
     <row r="10" spans="1:8" s="2" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="52">
+      <c r="A10" s="33">
         <v>1</v>
       </c>
-      <c r="B10" s="52" t="s">
+      <c r="B10" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="34">
+        <v>500</v>
+      </c>
+      <c r="E10" s="33"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="33" t="s">
         <v>30</v>
-      </c>
-      <c r="C10" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="53">
-        <v>500</v>
-      </c>
-      <c r="E10" s="52"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="52" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
